--- a/tests/eindhoven-500/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_Auto_OV_Fiets.xlsx
+++ b/tests/eindhoven-500/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_Auto_OV_Fiets.xlsx
@@ -895,7 +895,7 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>1.046292170658181</v>
+        <v>1.04629217065818</v>
       </c>
       <c r="C32">
         <v>0.8151746156947915</v>
@@ -1728,7 +1728,7 @@
         <v>80</v>
       </c>
       <c r="B81">
-        <v>0.9874870185077534</v>
+        <v>0.9874870185077536</v>
       </c>
       <c r="C81">
         <v>1.096022867159728</v>
@@ -4839,7 +4839,7 @@
         <v>263</v>
       </c>
       <c r="B264">
-        <v>0.547732947946552</v>
+        <v>0.5477329479465519</v>
       </c>
       <c r="C264">
         <v>0.4635027507596261</v>
@@ -4890,7 +4890,7 @@
         <v>266</v>
       </c>
       <c r="B267">
-        <v>0.3397562452462323</v>
+        <v>0.3397562452462322</v>
       </c>
       <c r="C267">
         <v>0.4654485814356898</v>
@@ -4941,7 +4941,7 @@
         <v>269</v>
       </c>
       <c r="B270">
-        <v>0.6336281921428406</v>
+        <v>0.6336281921428405</v>
       </c>
       <c r="C270">
         <v>0.807950340024757</v>
